--- a/log/db_log.xlsx
+++ b/log/db_log.xlsx
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -779,6 +779,30 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-03-29 17:51:19</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Người dùng root đã Đăng nhập hệ thống thành công</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-03-29 18:22:11</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Người dùng root đã Đăng nhập hệ thống thành công</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/log/db_log.xlsx
+++ b/log/db_log.xlsx
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -803,6 +803,210 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-03-31 08:17:18</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Người dùng root đã Đăng nhập hệ thống thành công</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-03-31 09:08:40</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Người dùng root đã Đăng nhập hệ thống thành công</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-03-31 14:05:05</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Người dùng root đã Đăng nhập hệ thống thành công</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-03-31 14:24:01</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Người dùng root đã Đăng nhập hệ thống thành công</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-03-31 14:24:40</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Người dùng root đã Đăng nhập hệ thống thành công</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-03-31 15:09:04</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Người dùng root đã Đăng nhập hệ thống thành công</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-03-31 15:15:48</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Người dùng root đã Import 20 sản phẩm vào Tồn CSR Có chứng từ</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-03-31 15:18:13</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Người dùng root đã Import 9 sản phẩm vào danh sách Hàng Không Chứng Từ</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-03-31 15:22:37</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Người dùng root đã Import 9 sản phẩm vào danh sách Hàng Không Chứng Từ</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-03-31 15:26:42</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Người dùng root đã Đăng nhập hệ thống thành công</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-03-31 15:27:55</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Người dùng root đã Import 9 sản phẩm vào danh sách Hàng Không Chứng Từ</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-03-31 15:40:22</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Người dùng root đã Import 11 sản phẩm vào danh sách Hàng Không Chứng Từ</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-03-31 15:43:24</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Người dùng root cập nhật 1 SP (Nhập kho HCNS): [8936233680318 |  | Nhập xuất: 8 | Tồn Cập nhật: 0]</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-03-31 15:43:50</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Người dùng root cập nhật 1 SP (Nhập kho HCNS): [None |  | Nhập xuất: 34 | Tồn Cập nhật: 0]</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-03-31 15:55:16</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Người dùng root đã Import 23 sản phẩm vào danh sách Tiêu Hủy</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-03-31 16:05:06</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Người dùng root đã Import 103 sản phẩm vào danh sách Nhập kho HCNS</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-03-31 16:58:39</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Người dùng root đã Đăng nhập hệ thống thành công</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/log/db_log.xlsx
+++ b/log/db_log.xlsx
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B45"/>
+  <dimension ref="A1:B74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1007,6 +1007,354 @@
         </is>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-04-01 09:53:19</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Người dùng root đã Đăng nhập hệ thống thành công</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-04-01 12:01:03</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Người dùng root đã Đăng nhập hệ thống thành công</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-04-01 13:42:05</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Người dùng root đã Đăng nhập hệ thống thành công</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-04-02 10:20:49</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Người dùng root đã Đăng nhập hệ thống thành công</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-04-02 10:28:29</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Người dùng root đã Import 556 sản phẩm mới vào danh sách Thu hồi Boxme (Bỏ qua 0 lỗi)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-04-02 10:51:50</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Người dùng root đã Import 103 sản phẩm vào danh sách Nhập kho HCNS</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-04-02 10:53:28</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Người dùng root đã Đăng nhập hệ thống thành công</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-04-02 10:54:05</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Người dùng root đã Import 23 sản phẩm vào danh sách Tiêu Hủy</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-04-02 10:54:43</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Người dùng root cập nhật 1 SP (Nhập kho HCNS): [None |  | Nhập xuất: 3 | Tồn Cập nhật: -2]</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-04-02 13:05:09</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Người dùng root đã Đăng nhập hệ thống thành công</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-04-02 13:06:41</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Người dùng root cập nhật 1 SP (Nhập kho HCNS): [None |  | Nhập xuất: 20 | Tồn Cập nhật: 14]</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-04-02 13:06:53</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Người dùng root cập nhật 1 SP (Nhập kho HCNS): [None |  | Nhập xuất: 0 | Tồn Cập nhật: 34]</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-04-02 13:22:18</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Người dùng root cập nhật 1 SP (Tồn CSR có chứng từ): [8936233680172 | SL: 6 | HSD: None | Note: ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-04-02 13:57:32</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Người dùng root cập nhật 1 SP (Tồn CSR có chứng từ): [8809563069286 | SL: 2 | HSD: 2027-10-30 | Note: ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-04-02 14:00:03</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Người dùng root cập nhật 1 SP (Tồn CSR có chứng từ): [8936233680172 | SL: 6 | HSD: None | Note: ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-04-02 14:01:29</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Người dùng root cập nhật 1 SP (Tồn CSR có chứng từ): [8809563069286 | SL: 2 | HSD: None | Note: ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-04-02 14:02:53</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Người dùng root cập nhật 1 SP (Tồn CSR có chứng từ): [8936233680172 | SL: 5 | HSD: None | Note: ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-04-02 14:40:07</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Người dùng root cập nhật 1 SP (Tồn CSR có chứng từ): [8936233680172 | SL: 6 | HSD: None | Note: ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-04-02 14:42:48</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Người dùng root đã Đăng nhập hệ thống thành công</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-04-02 14:42:58</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Người dùng root cập nhật 1 SP (Tồn CSR có chứng từ): [8936233680172 | SL: 1 | HSD: None | Note: ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-04-02 14:43:07</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Người dùng root cập nhật 1 SP (Tồn CSR có chứng từ): [8936233680172 | SL: 4 | HSD: None | Note: ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-04-02 14:45:50</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Người dùng root đã Đăng nhập hệ thống thành công</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-04-02 15:00:04</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Người dùng root đã Đăng nhập hệ thống thành công</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-04-02 15:02:44</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Người dùng root cập nhật 1 SP (Tiêu Huỷ): [8809783326824 | SL: 5 | HSD: 2026-08-03]</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-04-02 15:02:54</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Người dùng root cập nhật 1 SP (Tiêu Huỷ): [8809783326824 | SL: 3 | HSD: 2026-08-03]</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-04-02 15:13:10</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Người dùng root đã Đăng nhập hệ thống thành công</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-04-02 15:13:44</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Người dùng root cập nhật 1 SP (Tiêu Huỷ): [8809820740941 | SL: 1 | HSD: 2026-07-16]</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-04-02 15:18:57</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Người dùng root cập nhật 1 SP (Tiêu Huỷ): [8809820740941 | SL: 1 | HSD: 2026-07-16]</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-04-02 15:23:32</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Người dùng root đã Đăng nhập hệ thống thành công</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/log/db_log.xlsx
+++ b/log/db_log.xlsx
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B74"/>
+  <dimension ref="A1:B79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1355,6 +1355,66 @@
         </is>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-04-03 10:08:01</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Người dùng root đã Đăng nhập hệ thống thành công</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-04-03 14:33:53</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Người dùng root đã Đăng nhập hệ thống thành công</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-04-03 14:34:29</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Người dùng root đã Đăng nhập hệ thống thành công</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-04-03 14:36:14</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Người dùng root đã Đăng nhập hệ thống thành công</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-04-03 15:59:18</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Người dùng root đã Đăng nhập hệ thống thành công</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/log/db_log.xlsx
+++ b/log/db_log.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="user" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="users" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="log" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:Q3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,6 +440,81 @@
           <t>password</t>
         </is>
       </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>full_name</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>is_active</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>is_superadmin</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>perm_report</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>perm_thu_hoi_boxme</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>perm_nhap_kho_hcns</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>perm_hang_ton_csr</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>perm_hcns_khong_ct</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>perm_tieu_huy</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>perm_template</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>perm_system_logs</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>perm_about</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>perm_user_mgmt</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>session_version</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -449,7 +524,161 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>root</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -464,7 +693,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B79"/>
+  <dimension ref="A1:B111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1415,6 +1644,390 @@
         </is>
       </c>
     </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-04-06 14:05:00</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>[root] Đăng nhập hệ thống thành công</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-04-06 14:11:00</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>[root] Tạo tài khoản mới: thanhnhu</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-04-06 14:11:14</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>[root] Đăng xuất hệ thống</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-04-06 14:11:18</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>[thanhnhu] Đăng nhập hệ thống thành công</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-04-06 14:13:14</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>[thanhnhu] Đăng xuất hệ thống</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-04-06 14:13:19</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>[root] Đăng nhập hệ thống thành công</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-04-06 14:13:54</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>[root] Cập nhật tài khoản: root</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-04-06 14:13:57</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>[root] Đăng xuất hệ thống</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-04-06 14:14:02</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>[thanhnhu] Đăng nhập hệ thống thành công</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-04-06 14:14:07</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>[thanhnhu] Đăng xuất hệ thống</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-04-06 14:14:13</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>[root] Đăng nhập hệ thống thành công</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-04-06 14:14:31</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>[root] Cập nhật tài khoản: thanhnhu</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-04-06 14:14:32</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>[root] Cập nhật tài khoản: thanhnhu</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-04-06 14:14:35</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>[root] Cập nhật tài khoản: thanhnhu</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-04-06 14:14:35</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>[root] Cập nhật tài khoản: thanhnhu</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-04-06 14:17:07</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>[root] Cập nhật tài khoản: thanhnhu</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-04-06 14:19:01</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>[root] Cập nhật tài khoản: root</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-04-06 14:19:07</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>[root] Cập nhật tài khoản: thanhnhu</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-04-06 14:20:34</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>[root] Cập nhật tài khoản: root</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-04-06 14:23:31</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>[thanhnhu] Đăng nhập hệ thống thành công</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-04-06 14:24:37</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>[root] Cập nhật tài khoản: thanhnhu</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-04-06 14:25:38</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>[thanhnhu] Đăng xuất hệ thống</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-04-06 14:26:03</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>[root] Cập nhật tài khoản: root</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-04-06 14:26:06</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>[root] Đăng xuất hệ thống</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-04-06 14:26:09</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>[root] Đăng nhập hệ thống thành công</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-04-06 16:03:39</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>[root] Đăng nhập hệ thống thành công</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-04-06 16:04:49</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>[root] Đăng xuất hệ thống</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-04-06 16:05:37</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>[root] Đăng nhập hệ thống thành công</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-04-06 16:21:05</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>[root] Đăng xuất hệ thống</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-04-06 16:25:40</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>[root] Đăng nhập hệ thống thành công</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-04-06 16:25:49</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>[root] Đăng xuất hệ thống</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-04-06 16:27:51</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>[root] Đăng nhập hệ thống thành công</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/log/db_log.xlsx
+++ b/log/db_log.xlsx
@@ -693,7 +693,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B111"/>
+  <dimension ref="A1:B115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2028,6 +2028,54 @@
         </is>
       </c>
     </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-04-10 11:12:57</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>[root] Đăng nhập hệ thống thành công</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-04-10 11:15:19</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>[root] Đăng nhập hệ thống thành công</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-04-10 11:17:23</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>[root] Đăng nhập hệ thống thành công</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-04-10 13:12:35</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>[root] Đăng nhập hệ thống thành công</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
